--- a/samples/turnos_ejemplo_con_errores.xlsx
+++ b/samples/turnos_ejemplo_con_errores.xlsx
@@ -52,7 +52,7 @@
     <x:t>Error: no existe ningún colaborador con ese email.</x:t>
   </x:si>
   <x:si>
-    <x:t>19/10/2026</x:t>
+    <x:t>19/10/2027</x:t>
   </x:si>
   <x:si>
     <x:t>Error: la fecha está escrita como texto en un formato que no se entiende (usa una celda de fecha o yyyy-MM-dd).</x:t>
@@ -523,7 +523,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="4">
-        <x:v>46314</x:v>
+        <x:v>46679</x:v>
       </x:c>
       <x:c r="C2" s="5">
         <x:v>0.333333333333333</x:v>
@@ -540,7 +540,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="4">
-        <x:v>46314</x:v>
+        <x:v>46679</x:v>
       </x:c>
       <x:c r="C3" s="5">
         <x:v>0.5</x:v>
@@ -557,7 +557,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="4">
-        <x:v>46314</x:v>
+        <x:v>46679</x:v>
       </x:c>
       <x:c r="C4" s="5">
         <x:v>0.333333333333333</x:v>
@@ -574,7 +574,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="4">
-        <x:v>46314</x:v>
+        <x:v>46679</x:v>
       </x:c>
       <x:c r="C5" s="5">
         <x:v>0.333333333333333</x:v>
@@ -608,7 +608,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B7" s="4">
-        <x:v>46315</x:v>
+        <x:v>46680</x:v>
       </x:c>
       <x:c r="C7" s="5">
         <x:v>0.333333333333333</x:v>
@@ -622,7 +622,7 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="B8" s="4">
-        <x:v>46315</x:v>
+        <x:v>46680</x:v>
       </x:c>
       <x:c r="C8" s="5">
         <x:v>0.333333333333333</x:v>
@@ -639,7 +639,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="4">
-        <x:v>46315</x:v>
+        <x:v>46680</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>18</x:v>
@@ -656,7 +656,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="4">
-        <x:v>46315</x:v>
+        <x:v>46680</x:v>
       </x:c>
       <x:c r="D10" s="5">
         <x:v>0.666666666666667</x:v>
@@ -670,7 +670,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B11" s="4">
-        <x:v>46316</x:v>
+        <x:v>46681</x:v>
       </x:c>
       <x:c r="C11" s="5">
         <x:v>0.916666666666667</x:v>
